--- a/HONE_Test_Plan_AC_ACC.xlsx
+++ b/HONE_Test_Plan_AC_ACC.xlsx
@@ -1812,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2154,182 @@
       </c>
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Il focus si accende</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Serve un'auto e una pista su cui hai GIÀ dei giri salvati: senza un giro di riferimento il focus non nasce. Fai 3-4 giri puliti di fila e guarda la riga Focus nell'overlay.</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Dopo il terzo giro pulito compare un focus: una curva e un tema (frenata, trazione, percorrenza, linea…). Se NON compare, fermati qui e segnalo: le prove 15, 16 e 17 vanno saltate, perché senza focus il coach parla come prima ed è giusto che lo faccia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Il patto: il coach dice la parola che userà</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Quando il focus viene annunciato a voce, a fine giro, ascolta la frase per intero.</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>La frase nomina il TEMA e fa un esempio di parola: «In pista ti dirò solo parole sulla frenata, tipo 'meno freno'». Se annuncia il focus senza dire cosa sentirai, è un difetto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>In pista senti parole, non frasi</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Con il focus attivo, guida 2-3 giri normali facendo apposta anche errori di temi DIVERSI da quello del focus: se il focus è la frenata, esci male da una curva.</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>I consigli di tecnica che senti sono parole corte (1-3 parole) e tutte del tema del focus. Gli errori degli altri temi non vengono DETTI: li ritrovi scritti nell'overlay e nel resoconto di fine giro. Se senti frasi intere di tecnica, o una parola di un altro tema, è un difetto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Sicurezza e box parlano comunque</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Con un focus attivo su un tema qualsiasi, provoca apposta un bloccaggio in staccata (freno fortissimo).</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>«Bloccaggio, alleggerisci il freno» lo senti lo stesso e per intero, anche se il bloccaggio non c'entra col tema del focus. Vale anche per pattinamento, benzina e chiamate ai box: il filtro non li tocca mai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Il briefing da fermo ai box</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Guida finché l'Ingegnere propone una modifica che si fa SOLO in garage (prova 11), poi rientra ai box e fermati davvero nella tua piazzola, a 0 km/h. Su ACC questa prova prima non poteva riuscire.</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Da fermo senti «Sei ai box. Apri la pagina Ingegnere nel browser: applica la proposta, scrivi il setup e ricaricalo dal garage prima di uscire». Se non arriva subito aspetta: si ripete ogni 8 secondi finché non viene detta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Nessun allarme mentre parcheggi</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Entra in corsia box e frena deciso per fermarti nella piazzola, come faresti in gara.</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Silenzio: nessun «bloccaggio», nessun «pattini in uscita». Prima gridava, perché una frenata con l'ABS a bassa velocità gli sembrava un bloccaggio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>L'overlay parte sullo schermo centrale</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Con i tre schermi uniti dal gioco, avvia HONE e guarda dove compare l'overlay. Poi chiudi il gioco e riaprilo: l'origine degli schermi si sposta, ed è lì che sbagliava.</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>L'overlay sta in alto a sinistra dello SCHERMO CENTRALE, non del monitor di sinistra, e ci torna da solo entro un secondo quando la geometria degli schermi cambia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Il coach è assillante o assente?</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>A fine sessione, da fermo. Non è una prova con un esito: è una domanda, e l'unico modo che abbiamo di rispondere.</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Rispondi: assillante / giusto / assente. Lo stesso consiglio non si ripete prima di 20 secondi, e quel numero non è mai stato misurato su nessuno — non esiste un modo di deciderlo che non sia questa risposta.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2175,7 +2351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2544,6 +2720,40 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>La debolezza che HONE ha deciso di farti lavorare adesso: una curva e un tema. Ne tiene UNA per volta, per cinque-sei giri, poi la dichiara migliorata o la parcheggia e passa alla successiva. È lo stesso ritmo che usano i coach veri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Parola-innesco</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>La parola corta che senti in pista al posto della frase intera — «più tardi», «rilascia», «gas». Serve perché mentre guidi la testa è occupata: una frase la perdi, una parola no. È concordata prima, quando il coach annuncia il focus, e resta sempre la stessa per quel tema. La frase per esteso la trovi a schermo e nel resoconto.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>

--- a/HONE_Test_Plan_AC_ACC.xlsx
+++ b/HONE_Test_Plan_AC_ACC.xlsx
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>L'overlay sta in alto a sinistra dello SCHERMO CENTRALE, non del monitor di sinistra, e ci torna da solo entro un secondo quando la geometria degli schermi cambia.</t>
+          <t>L'overlay sta in alto al CENTRO dello schermo centrale, non sul monitor di sinistra, e ci torna da solo entro un secondo quando la geometria degli schermi cambia. Il riquadro dei test sta in alto a SINISTRA e non lo copre: sono due finestre diverse.</t>
         </is>
       </c>
     </row>
